--- a/data/seed/portfolio/L-2025-0129/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-0129/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,82 +535,82 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>4294000</v>
+        <v>17635000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Ziyo Yog'och AJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>302698939</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000233659695001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shartnoma №3/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №184/26 от 01.07.2026</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>72094000</v>
+        <v>85435000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>2283000</v>
+        <v>5787000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Afrosiyob Mehmonxona AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>200567374</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000165773504001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2466 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №9878 от 01.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>74377000</v>
+        <v>91222000</v>
       </c>
     </row>
     <row r="10">
@@ -621,156 +621,156 @@
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7381000</v>
+        <v>2686000</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №167/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №211/26</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>66996000</v>
+        <v>88536000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>10767000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>4387000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4371</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №67/26, QQS bilan</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>77763000</v>
+        <v>84149000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>7775000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>3256000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №44/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1269</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>85538000</v>
+        <v>80893000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>7416000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>5334000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Shahrisabz Meva Eksport XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>303219199</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000285634616001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №90/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №5847</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>92954000</v>
+        <v>75559000</v>
       </c>
     </row>
     <row r="14">
@@ -782,35 +782,35 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>4427000</v>
+        <v>62235000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nihol Metall Servis MChJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>398026989</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000942336596001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №159/26 от 06.07.2026</t>
+          <t>Оплата по счет-фактуре №111 за поставленный товар</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>97381000</v>
+        <v>137794000</v>
       </c>
     </row>
     <row r="15">
@@ -820,178 +820,183 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>19337000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>12156000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Termiz Farm Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №9425</t>
+          <t>Оплата по счет-фактуре №2471 за поставленный товар</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>78044000</v>
+        <v>149950000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>8548000</v>
+        <v>11341000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nihol Metall Servis MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>398026989</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000942336596001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3177 07.07.2026, QQS bilan</t>
+          <t>Оплата по с/ф №5732 за поставленный товар</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>86592000</v>
+        <v>161291000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>1222000</v>
+        <v>4390000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>355903784</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000105213806001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №375 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №9082 запоставленный товар</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>87814000</v>
+        <v>165681000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>1846000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>4059000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahor Qurilish AJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>221524939</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000004926325001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №75/24</t>
+          <t>Предоплата за товар по дог. №131/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>85968000</v>
+        <v>169740000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>149304000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>2200000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ilhom Non MChJ</t>
+          <t>Guliston Trans Servis XK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>367476407</t>
+          <t>330832400</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000813740176001</t>
+          <t>20208000797817145001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1001,512 +1006,512 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №212/26</t>
+          <t>Оплата за товар по счет-фактуре №8287 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-63336000</v>
+        <v>171940000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>24835000</v>
+        <v>2110000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9390 08.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №95/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-38501000</v>
+        <v>174050000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>6514000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>19337000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Marg'ilon Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>338177050</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000960978337001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9795 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-31987000</v>
+        <v>154713000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3995000</v>
+        <v>1846000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>373374022</t>
+          <t>362839769</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000160291626001</t>
+          <t>20208000795021282001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №598</t>
+          <t>Арендная плата за июль 2026 г. по договору №7/22</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-35982000</v>
+        <v>152867000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46216</v>
+        <v>46210</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6430000</v>
+        <v>16270000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nukus Qog'oz AJ</t>
+          <t>Mehnat Yog'och MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>279032191</t>
+          <t>347640778</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000952856346001</t>
+          <t>20208000374017664001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №206/26</t>
+          <t>Оплата за сырье по договору №190/26 от 07.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-42412000</v>
+        <v>136597000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>10217000</v>
+        <v>18585000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7183 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №9081 за поставленный товар</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-32195000</v>
+        <v>155182000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>6570000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>3157000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>242198319</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000412271299001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9430 14.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №85/26 от 09.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-25625000</v>
+        <v>152025000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>1205000</v>
+        <v>22722000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1592 14.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №118/26 от 10.07.2026</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-24420000</v>
+        <v>174747000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>1806000</v>
+        <v>8502000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №42/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №122/26, НДС 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>-22614000</v>
+        <v>183249000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>26200000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>13421000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0129)</t>
+          <t>Termiz Farm Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16307000349582326417</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0129 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товар по счет-фактуре №1649 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>-48814000</v>
+        <v>196670000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>2499000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>5699000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №149/26</t>
+          <t>Оплата за продукцию по дог. №282/26, НДС 12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>-51313000</v>
+        <v>202369000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>2637000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>3488000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Оплата за продукцию по договору №138/26, НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>-53950000</v>
+        <v>205857000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>2637000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>2819000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Предоплата за товар по договору №93/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>-56587000</v>
+        <v>208676000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>36049000</v>
+        <v>2813000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1516,37 +1521,37 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Shartnoma №136/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №297/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>-20538000</v>
+        <v>211489000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>2012000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>3754000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1556,237 +1561,232 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Shartnoma №31/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №180/26</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>-18526000</v>
+        <v>207735000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>1778000</v>
+        <v>5512000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6148</t>
+          <t>Shartnoma №11/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>-16748000</v>
+        <v>213247000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>1426000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>2637000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nihol Metall Servis AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>297429962</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000496807543001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6715</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>-15322000</v>
+        <v>210610000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>10911000</v>
+        <v>2637000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №216/26</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>-26233000</v>
+        <v>207973000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2439000</v>
+        <v>3388000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Marg'ilon Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>242198319</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000412271299001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4209</t>
+          <t>Xom ashyo uchun to'lov, shartn. №230/26, QQS bilan</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>-28672000</v>
+        <v>204585000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46224</v>
+        <v>46218</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3114000</v>
+        <v>26200000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0129)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000349582326417</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Kredit shartnomasi L-2025-0129 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>-31786000</v>
+        <v>178385000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>2373000</v>
+        <v>2551000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Xiva Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>256737481</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000577350430001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1796,37 +1796,37 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5581</t>
+          <t>Mahsulot uchun to'lov, shartnoma №59/26, QQS 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>-29413000</v>
+        <v>180936000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>1297000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>1878000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1836,157 +1836,157 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №70/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №57/26</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>-28116000</v>
+        <v>179058000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>52555000</v>
+        <v>3473000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4193 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №153/26, НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>24439000</v>
+        <v>182531000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>13164000</v>
+        <v>14755000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4618</t>
+          <t>Mahsulot uchun to'lov, shartnoma №74/26, QQS 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>37603000</v>
+        <v>197286000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>1154000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>12801000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000302373047001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Оплата за товар по счет-фактуре №1493 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>36449000</v>
+        <v>210087000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>3342000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>2821000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1996,237 +1996,237 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №131/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №196/26, НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>33107000</v>
+        <v>212908000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>19219000</v>
+        <v>2357000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Oqtosh Meva Eksport XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>205192254</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000975353245001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7230</t>
+          <t>Оплата за товар по счет-фактуре №2933 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>52326000</v>
+        <v>215265000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>10364000</v>
+        <v>3246000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №153/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6727 21.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>62690000</v>
+        <v>218511000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>7043000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>3041000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5585</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>69733000</v>
+        <v>215470000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>1489000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>60919000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Shartnoma №47/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №17/26</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>71222000</v>
+        <v>154551000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>1274000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>1154000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Marg'ilon Meva Eksport MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>338177050</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000960978337001</t>
+          <t>20208000932152493001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Shartnoma №142/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>72496000</v>
+        <v>153397000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>1678000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>3470000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2236,197 +2236,197 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3926 28.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №1266</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>74174000</v>
+        <v>149927000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>1634000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>3736000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>355903784</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000105213806001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №137/26, QQS bilan</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>75808000</v>
+        <v>146191000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>3230000</v>
+        <v>9852000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №43/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №2387</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>72578000</v>
+        <v>136339000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>3301000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>20430000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SHARTNOMA №150/26 BO'YICHA OLDINDN TO'LOV</t>
+          <t>Предоплата за материалы по договору №149/26</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>75879000</v>
+        <v>115909000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>5357000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>2897000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №29826, QQS bilan</t>
+          <t>Оплата по счет-фактуре №1327 за поставленный товар</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>70522000</v>
+        <v>118806000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>4926000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>2172000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2436,32 +2436,37 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №161/26 от 31.07.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №213/26, QQS bilan</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>75448000</v>
+        <v>116634000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>300000</v>
+        <v>5061000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Farg'ona Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2471,37 +2476,37 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за сырье по договору №111/26 от 29.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>75148000</v>
+        <v>111573000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>9686000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>5808000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2511,312 +2516,312 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3896 03.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №5039</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>84834000</v>
+        <v>105765000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>2061000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>11115000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9279 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №143/26 от 29.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>86895000</v>
+        <v>94650000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>53580000</v>
+        <v>13500000</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nukus Qog'oz AJ</t>
+          <t>Durdona Poligraf MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>279032191</t>
+          <t>323686468</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000952856346001</t>
+          <t>20208000750412014001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №269/26</t>
+          <t>Предоплата за материалы по договору №117/26</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>33315000</v>
+        <v>81150000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>20361000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>3070000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №1135</t>
+          <t>Оплата за товар по счет-фактуре №2131 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>12954000</v>
+        <v>84220000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>15268000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>296269949</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2698</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28222000</v>
+        <v>83920000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46240</v>
+        <v>46234</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>3092000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>4317000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №241/26</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>31314000</v>
+        <v>79603000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>1944000</v>
+        <v>6047000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bahor Qurilish AJ</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>221524939</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000004926325001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnoma №75/24</t>
+          <t>Оплата за сырье по договору №19/26 от 31.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>29370000</v>
+        <v>73556000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>2271000</v>
+        <v>4024000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7713 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №854 за поставленный товар</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>31641000</v>
+        <v>77580000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>2352000</v>
+        <v>3310000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nihol Metall Servis AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>297429962</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000496807543001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2826,152 +2831,157 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №271/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №7742 за поставленный товар</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>33993000</v>
+        <v>80890000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46248</v>
+        <v>46237</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>2777000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>2248000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Shartnoma №14/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>31216000</v>
+        <v>83138000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46248</v>
+        <v>46237</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>2777000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>2064000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Оплата за товар по счет-фактуре №3896 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28439000</v>
+        <v>85202000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46248</v>
+        <v>46237</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>22280000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>683000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Shodlik Yog'och MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>317705059</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000097833700001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №37/26</t>
+          <t>Оплата по счет-фактуре №1467 за поставленный товар</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6159000</v>
+        <v>85885000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46249</v>
+        <v>46238</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>26200000</v>
+        <v>4181000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0129)</t>
+          <t>Farg'ona Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>16307000349582326417</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2981,397 +2991,392 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0129 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за материалы по дог. №94/26</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>-20041000</v>
+        <v>81704000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46251</v>
+        <v>46238</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>16727000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>16659000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>242198319</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000412271299001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №281/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №77/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>-3314000</v>
+        <v>65045000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46255</v>
+        <v>46238</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>21713000</v>
+        <v>20361000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>227236864</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №145/26</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>-25027000</v>
+        <v>44684000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>21405000</v>
+        <v>3613000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1613 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №5187 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>-3622000</v>
+        <v>48297000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>5127000</v>
+        <v>2992000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8775</t>
+          <t>Оплата по счет-фактуре №9054 за поставленный товар</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1505000</v>
+        <v>51289000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46258</v>
+        <v>46239</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>3249000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>2360000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА ИЮЛЬ</t>
+          <t>Оплата по счет-фактуре №2399 за поставленный товар</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>-1744000</v>
+        <v>53649000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46259</v>
+        <v>46239</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>170484000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>4335000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №224/26, QQS 12%</t>
+          <t>Оплата за упаковочны материалы, с/ф №1428</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>168740000</v>
+        <v>49314000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46259</v>
+        <v>46240</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>2405000</v>
+        <v>4811000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>355903784</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000105213806001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5887</t>
+          <t>Оплата за продукцию по договору №14/26, НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>171145000</v>
+        <v>54125000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46259</v>
+        <v>46240</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>1215000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>4019000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000302373047001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Оплата за продукцию по договору №174/26, НДС 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>169930000</v>
+        <v>58144000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46260</v>
+        <v>46240</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>8094000</v>
+        <v>699000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Oqtosh Meva Eksport XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>205192254</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000975353245001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №87/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №295/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>178024000</v>
+        <v>58843000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46260</v>
+        <v>46240</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>3217000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>5665000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Toshkent Tekstil MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>367686567</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000332852864001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3381,37 +3386,37 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8128</t>
+          <t>Оплата за товары согласно счет-фактуре №2727</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>181241000</v>
+        <v>53178000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46260</v>
+        <v>46241</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>2957000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>1944000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>355903784</t>
+          <t>362839769</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000105213806001</t>
+          <t>20208000795021282001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3421,37 +3426,37 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4510 от 26.08.2026, в т.ч. НДС 12%</t>
+          <t>Аренда помещения за август, дог. №7/22</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>184198000</v>
+        <v>51234000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>3319000</v>
+        <v>962000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Xiva Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>256737481</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000577350430001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3461,77 +3466,77 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SHARTNOMA №132/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №97/26, НДС 12%</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>187517000</v>
+        <v>52196000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46262</v>
+        <v>46244</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>24023000</v>
+        <v>10525000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Poligraf MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>296283976</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000379502128001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5894</t>
+          <t>Оплата за сырье по договору №75/26 от 10.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>163494000</v>
+        <v>41671000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>2300000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>12824000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv MChJ</t>
+          <t>Shahrisabz Meva Eksport XK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>280051922</t>
+          <t>303219199</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000489753532001</t>
+          <t>20208000285634616001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3541,392 +3546,392 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №150/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №5630</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>165794000</v>
+        <v>28847000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46265</v>
+        <v>46246</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>649000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>BANK XIZMATI UCHUN KOMISSIYA</t>
+          <t>Оплата по с/ф №2186 за поставленный товар</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>165494000</v>
+        <v>29496000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46265</v>
+        <v>46246</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>11726000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>644000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nukus Qog'oz AJ</t>
+          <t>Shodlik Yog'och MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>279032191</t>
+          <t>317705059</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000952856346001</t>
+          <t>20208000097833700001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №144/26, QQS bilan</t>
+          <t>Оплата по с/ф №7763 за поставленный товар</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>153768000</v>
+        <v>30140000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46265</v>
+        <v>46247</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>14940000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>2177000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ilhom Non MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>367476407</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000813740176001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8168</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2025</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>138828000</v>
+        <v>32317000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>16711000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>3569000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Xiva Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>256737481</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000577350430001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договру №191/26 от 31.08.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6873</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>122117000</v>
+        <v>35886000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>20009000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>2662000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>373374022</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000160291626001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8862</t>
+          <t>Оплата за товар по с/ф №5466 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>102108000</v>
+        <v>38548000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>27210000</v>
+        <v>2777000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ilhom Non MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>367476407</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000813740176001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №77/26</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>74898000</v>
+        <v>35771000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46267</v>
+        <v>46248</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>4842000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>2777000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2114 02.09.2026, QQS bilan</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>79740000</v>
+        <v>32994000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46267</v>
+        <v>46248</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>10295000</v>
+        <v>3710000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>373374022</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000160291626001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №114/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №8106</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>69445000</v>
+        <v>29284000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46268</v>
+        <v>46248</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>4482000</v>
+        <v>6973000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Qo'qon Dori-Darmon MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>358968401</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000996615063001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №231/26, QQS bilan</t>
+          <t>Предоплата за материалы по договору №179/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>64963000</v>
+        <v>22311000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46269</v>
+        <v>46249</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>146956000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>26200000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>310709224</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0129)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>16307000349582326417</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3936,77 +3941,77 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Shartnoma №32/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2025-0129 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>211919000</v>
+        <v>-3889000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46269</v>
+        <v>46251</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>4026000</v>
+        <v>1883000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №260/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>215945000</v>
+        <v>-2006000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46269</v>
+        <v>46251</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>1097000</v>
+        <v>1511000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Xiva Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>256737481</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000577350430001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4016,272 +4021,277 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Shartnoma №11/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №102/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>217042000</v>
+        <v>-495000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46272</v>
+        <v>46251</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>4614000</v>
+        <v>828000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №225/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9337 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>221656000</v>
+        <v>333000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46272</v>
+        <v>46251</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>1742000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>5449000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6579</t>
+          <t>Tovarlar uchun to'lov h/f №5247</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>223398000</v>
+        <v>-5116000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46272</v>
+        <v>46251</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>1356000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>46731000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>355903784</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000105213806001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №8/26 от 07.09.2026</t>
+          <t>Предоплата за материалы по договору №209/26</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>224754000</v>
+        <v>-51847000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46272</v>
+        <v>46252</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>728000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>4191000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nihol Metall Servis MChJ</t>
+          <t>Toshkent Tekstil MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>398026989</t>
+          <t>367686567</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000942336596001</t>
+          <t>20208000332852864001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3941 07.09.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №74/26</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>225482000</v>
+        <v>-56038000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46272</v>
+        <v>46254</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>652000</v>
+        <v>147348000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5984 07.09.2026, QQS bilan</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №48/26 ОТ 20.08.2026</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>226134000</v>
+        <v>91310000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46272</v>
+        <v>46254</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>12811000</v>
+        <v>9198000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6115</t>
+          <t>Оплата за товары согласно счет-фактуре №317</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>213323000</v>
+        <v>82112000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46272</v>
+        <v>46254</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>20816000</v>
+        <v>12037000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Farg'ona Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4291,317 +4301,317 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №6652</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №155/26, QQS bilan</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>192507000</v>
+        <v>70075000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46273</v>
+        <v>46255</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>685000</v>
+        <v>23582000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Marg'ilon Meva Eksport MChJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>338177050</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000960978337001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №298/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №1983 от 21.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>193192000</v>
+        <v>93657000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46273</v>
+        <v>46255</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>1987000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>2260000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bahor Qurilish AJ</t>
+          <t>Marg'ilon Mebel AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>221524939</t>
+          <t>342996254</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000004926325001</t>
+          <t>20208000680754342001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>IJARA HAQI SENTYABR OYI UCHUN, SHARTNOMA №75/24</t>
+          <t>Оплата по счет-фактуре №1888 за поставленный товар</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>191205000</v>
+        <v>95917000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46273</v>
+        <v>46258</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>3465000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>8746000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ilhom Non MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>367476407</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000813740176001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9333</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1613</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>187740000</v>
+        <v>104663000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46273</v>
+        <v>46258</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>8686000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>826000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ilhom Non MChJ</t>
+          <t>Oqtosh Meva Eksport XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>367476407</t>
+          <t>205192254</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000813740176001</t>
+          <t>20208000975353245001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3955</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №118/26 ОТ 24.08.2026</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>179054000</v>
+        <v>105489000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46274</v>
+        <v>46258</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>4880000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>602000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ilhom Non MChJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>367476407</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000813740176001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №146/26</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5805 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>174174000</v>
+        <v>106091000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46275</v>
+        <v>46258</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>1415000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>3164000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1139 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>175589000</v>
+        <v>102927000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46275</v>
+        <v>46259</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>68093000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>5736000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Poligraf MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>296283976</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000379502128001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №133/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №3210 за поставленный товар</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>107496000</v>
+        <v>108663000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46276</v>
+        <v>46259</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>14532000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>720000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4611,472 +4621,477 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9164</t>
+          <t>Оплата за продукцию по договору №224/26, НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>92964000</v>
+        <v>109383000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46279</v>
+        <v>46260</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>4056000</v>
+        <v>3497000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №124 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №8128 за поставленный товар</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>97020000</v>
+        <v>112880000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46279</v>
+        <v>46260</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>2473000</v>
+        <v>737000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>355903784</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000105213806001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5942 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №148/26, НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>99493000</v>
+        <v>113617000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46279</v>
+        <v>46260</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>2300000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>24233000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>242198319</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000412271299001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Shartnoma №161/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно с/ф №403</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>101793000</v>
+        <v>89384000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46279</v>
+        <v>46261</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>1490000</v>
+        <v>599000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Shodlik Yog'och MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>317705059</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000097833700001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2937</t>
+          <t>Предоплата за товар по договору №7/26 от 27.08.2026</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>103283000</v>
+        <v>89983000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46279</v>
+        <v>46261</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>2839000</v>
+        <v>1215000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000932152493001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>100444000</v>
+        <v>88768000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46279</v>
+        <v>46262</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>2839000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>1104000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №132/26 ОТ 28.08.2026</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>97605000</v>
+        <v>89872000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46280</v>
+        <v>46265</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>5304000</v>
+        <v>6570000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Nihol Metall Servis MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>398026989</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000942336596001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №279/26 от 15.09.2026</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №98/26, НДС 12%</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>102909000</v>
+        <v>96442000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46280</v>
+        <v>46265</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>26200000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>4444000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-0129)</t>
+          <t>Oqtosh Meva Eksport XK</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>205192254</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>16307000349582326417</t>
+          <t>20208000975353245001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-0129 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за продукцию по договору №150/26, НДС 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>76709000</v>
+        <v>100886000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46282</v>
+        <v>46265</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>4322000</v>
+        <v>4144000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2688</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3525</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>81031000</v>
+        <v>105030000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46282</v>
+        <v>46265</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>1201000</v>
+        <v>3870000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Xiva Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>256737481</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000577350430001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3515 17.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №280/26, QQS 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>82232000</v>
+        <v>108900000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46283</v>
+        <v>46265</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>9353000</v>
+        <v>1659000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Marg'ilon Meva Eksport MChJ</t>
+          <t>Oqtosh Meva Eksport XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>338177050</t>
+          <t>205192254</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000960978337001</t>
+          <t>20208000975353245001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Shartnoma №242/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №153/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>91585000</v>
+        <v>110559000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>5560000</v>
+        <v>1524000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Xiva Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>256737481</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000577350430001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5086,117 +5101,112 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №277/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №2397 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>97145000</v>
+        <v>112083000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>5006000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>355903784</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000105213806001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №806 21.09.2026, QQS bilan</t>
+          <t>КОМИССИЯ ЗА ПЕРЕВОД</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>102151000</v>
+        <v>111783000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>3905000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>11258000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №40/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №295/26</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>106056000</v>
+        <v>100525000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>2477000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>29486000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5206,237 +5216,232 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №193/26 от 21.09.2026</t>
+          <t>Оплата за упаковочные маериалы, с/ф №489</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>108533000</v>
+        <v>71039000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46286</v>
+        <v>46266</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>1268000</v>
+        <v>3141000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Marg'ilon Meva Eksport MChJ</t>
+          <t>Shodlik Yog'och MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>338177050</t>
+          <t>317705059</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000960978337001</t>
+          <t>20208000097833700001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по дог. №64/26, НДС 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>109801000</v>
+        <v>74180000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46286</v>
+        <v>46267</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>1143000</v>
+        <v>1793000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Shartnoma №137/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №37/26, НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>110944000</v>
+        <v>75973000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46286</v>
+        <v>46268</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>606000</v>
+        <v>3602000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2876</t>
+          <t>Оплата за товар по счет-фактуре №9733 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>111550000</v>
+        <v>79575000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46286</v>
+        <v>46269</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>4707000</v>
+        <v>2259000</v>
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Poligraf MChJ</t>
+          <t>Yangi Hayot Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>296283976</t>
+          <t>390378441</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000379502128001</t>
+          <t>20208000521380672001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №255/26, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №170/26</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>106843000</v>
+        <v>77316000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46286</v>
+        <v>46269</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>14402000</v>
+        <v>20816000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>227236864</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №73/26, QQS bilan</t>
+          <t>Заработная плата за август 2026 г. (перечислениена пластиковые карты)</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>92441000</v>
+        <v>56500000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>15614000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>10656000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5446,37 +5451,37 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №87/26</t>
+          <t>Оплата за товар по счет-фактуре №2899 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>76827000</v>
+        <v>67156000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46287</v>
+        <v>46272</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>4536000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>7782000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5486,197 +5491,197 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №77</t>
+          <t>Оплата за сырье по договору №1/26 от 07.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>81363000</v>
+        <v>59374000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46287</v>
+        <v>46274</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>1372000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>1987000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bahor Polimer XK</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>389308324</t>
+          <t>362839769</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000067978171001</t>
+          <t>20208000795021282001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4698</t>
+          <t>Аренда помещения за сентябрь, дог. №7/22</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>82735000</v>
+        <v>57387000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46287</v>
+        <v>46274</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>6672000</v>
+        <v>3033000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Marg'ilon Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>242198319</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000412271299001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №118/26, QQS BILAN</t>
+          <t>Предоплата за материалы по договору №273/26</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>76063000</v>
+        <v>54354000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46288</v>
+        <v>46275</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>2936000</v>
+        <v>40680000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Mebel AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>342996254</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000680754342001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №80/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №5522 за поставленный товар</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>78999000</v>
+        <v>95034000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46288</v>
+        <v>46276</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>3261000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>13858000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>Оплата за продукцию по договору №274/26, НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>75738000</v>
+        <v>108892000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46288</v>
+        <v>46279</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>13475000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>17396000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5686,37 +5691,37 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №57/26, QQS bilan</t>
+          <t>ОПЛАТА ПО С/Ф №3935 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>62263000</v>
+        <v>126288000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>13379000</v>
+        <v>7454000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Shodlik Yog'och MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>317705059</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000097833700001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5726,277 +5731,272 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f 513 24.09.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №220 за поставленный товар</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>75642000</v>
+        <v>133742000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>1887000</v>
+        <v>5927000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz XK</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>296269949</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000612973678001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №81/26, QQS 12%</t>
+          <t>Оплата по с/ф №3682 за поставленный товар</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>77529000</v>
+        <v>139669000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>603000</v>
+        <v>2643000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2667</t>
+          <t>Оплата за продукцию по договору №160/26, НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>78132000</v>
+        <v>142312000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>8655000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>1932000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ilhom Non MChJ</t>
+          <t>Marg'ilon Mebel AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>367476407</t>
+          <t>342996254</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000813740176001</t>
+          <t>20208000680754342001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №187/26</t>
+          <t>Предоплата за товар по договору №298/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>69477000</v>
+        <v>144244000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46290</v>
+        <v>46279</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>1247000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>16922000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Nihol Metall Servis AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>297429962</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000496807543001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Shartnoma №36/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №2462</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>70724000</v>
+        <v>127322000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46290</v>
+        <v>46279</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1242000</v>
+        <v>173021000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oltin Vodiy Tikuv XK</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>275340041</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000302373047001</t>
+          <t>20208000547484199001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ELEKTR ENERGIYASI UCHUN TO'LOV</t>
+          <t>Предоплата за материалы по договору №126/26</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>69482000</v>
+        <v>-45699000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46290</v>
+        <v>46280</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>7494000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>2297000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Poligraf MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>296283976</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000379502128001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №224/26</t>
+          <t>Оплата за продукцию по договору №56/26, НДС 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>61988000</v>
+        <v>-43402000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46293</v>
+        <v>46280</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>9115000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>26200000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>310709224</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-0129)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>16307000349582326417</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6006,277 +6006,277 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8614 28.09.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-0129 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>71103000</v>
+        <v>-69602000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>4414000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>2839000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Marg'ilon Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>338177050</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000960978337001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №245/26, QQS 12%</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>75517000</v>
+        <v>-72441000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46293</v>
+        <v>46281</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>3097000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>2839000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №94/26, QQS 12%</t>
+          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I AVGUST 2026</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>78614000</v>
+        <v>-75280000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>2341000</v>
+        <v>8094000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Shartnoma №30/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №239/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>80955000</v>
+        <v>-67186000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>9701000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>4801000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Tong Avto Savdo MChJ</t>
+          <t>Oqtosh Meva Eksport XK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>373374022</t>
+          <t>205192254</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000160291626001</t>
+          <t>20208000975353245001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6717</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №476</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>71254000</v>
+        <v>-62385000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>4364000</v>
+        <v>4415000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv MChJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>280051922</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000489753532001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1140 29.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №1637 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>75618000</v>
+        <v>-57970000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>1622000</v>
+        <v>4172000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Navro'z Tikuv MChJ</t>
+          <t>Termiz Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>280051922</t>
+          <t>326994906</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000489753532001</t>
+          <t>20208000297367858001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Shartnoma №183/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по дог. №110/26, НДС 12%</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>77240000</v>
+        <v>-53798000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>726000</v>
+        <v>2387000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Marg'ilon Meva Eksport MChJ</t>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>338177050</t>
+          <t>270922476</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000960978337001</t>
+          <t>20208000611193095001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6286,77 +6286,77 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №230/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №6437 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>77966000</v>
+        <v>-51411000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>5343000</v>
+        <v>2176000</v>
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nukus Qog'oz AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>279032191</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000952856346001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №288/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №9602</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>72623000</v>
+        <v>-53587000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>1512000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>5904000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Guliston Savdo AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>310709224</t>
+          <t>381422341</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000656111930001</t>
+          <t>20208000250559016001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6366,32 +6366,37 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №266/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №33/26</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>74135000</v>
+        <v>-59491000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46295</v>
+        <v>46287</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>9502000</v>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Xiva Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>256737481</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000577350430001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6401,76 +6406,591 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата по счет-фактуре №7474 за поставленный товар</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>73835000</v>
+        <v>-49989000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46295</v>
+        <v>46287</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>8335000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>8684000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sharq Trans Servis MChJ</t>
+          <t>Guliston Trans Servis XK</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>227236864</t>
+          <t>330832400</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000837504120001</t>
+          <t>20208000797817145001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №291/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>-41305000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>3247000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>НДС за август 2026 г.</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>-44552000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>38118000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Termiz Farm Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>326994906</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000297367858001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №3802 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>-6434000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>5592000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Farg'ona Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>381422341</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000250559016001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №263/26</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>-12026000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>30958000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Termiz Farm Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>326994906</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000297367858001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №35/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>18932000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>3431000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>270922476</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000611193095001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
           <t>01204</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №9495</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №118/26 от 25.09.2026</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>22363000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>5513000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>270922476</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000611193095001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №4384 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>27876000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>2098000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Termiz Farm Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>326994906</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000297367858001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Shartnoma №89/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>29974000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>1242000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000932152493001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>28732000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>17883000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>270922476</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000611193095001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №40/26 от 29.09.2026</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>46615000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>3379000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Marg'ilon Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>270922476</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000611193095001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №96/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>49994000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>10083000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Oqtosh Meva Eksport XK</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>205192254</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000975353245001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>TOVAR UCHUN TO'LOV, H/F №2338 30.09.2026, QQS BILAN</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>60077000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>5723000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Oqtosh Meva Eksport XK</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>205192254</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000975353245001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №195/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>65800000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Yangi Asr Bank</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Комиссия банка за расчетно-кассоое обслуживание за сентябрь</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
         <v>65500000</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C157" s="4" t="n">
-        <v>804254000</v>
-      </c>
-      <c r="D157" s="4" t="n">
-        <v>801954000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="C170" s="4" t="n">
+        <v>790041000</v>
+      </c>
+      <c r="D170" s="4" t="n">
+        <v>787741000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C158" s="4" t="n">
+      <c r="C171" s="4" t="n">
         <v>65500000</v>
       </c>
-      <c r="D158" s="4" t="n"/>
+      <c r="D171" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
